--- a/pivot-smoke.xlsx
+++ b/pivot-smoke.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Занято" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Курс" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Связанные" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,4 +975,316 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Курс</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Город</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Новая</t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>900*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Иванов</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>1200*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Иванов</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Закрыта</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>450*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Сидоров</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Закрыта</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>1400*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Петрова</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Новая</t>
+        </is>
+      </c>
+      <c r="C6">
+        <f>700*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Петрова</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="C7">
+        <f>250*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Иванов</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Закрыта</t>
+        </is>
+      </c>
+      <c r="C8">
+        <f>800*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Сидоров</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Казань</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Новая</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>400*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Петрова</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Омск</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Новая</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>1500*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Сидоров</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Омск</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="C11">
+        <f>1100*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Иванов</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Омск</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Закрыта</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>1300*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Петрова</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Омск</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Новая</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>1000*Курс!$B$1</f>
+        <v/>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Сидоров</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>